--- a/Advexcel/Looking up the value INDEX MATCH - Stu.xlsx
+++ b/Advexcel/Looking up the value INDEX MATCH - Stu.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30326"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11004"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\hp\Desktop\Jul25-N305 DSDA\Excel\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/karan/Desktop/EXCEL ITVEDANT/Advexcel/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2FF4D7DB-E6AE-4E4A-9D4C-F4D12ACEE5F0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2FCE32CF-70C6-0741-A9D0-D916E5029406}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10420" firstSheet="2" activeTab="7" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="660" windowWidth="29400" windowHeight="18460" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="INDEX" sheetId="2" r:id="rId1"/>
@@ -22,17 +22,55 @@
     <sheet name="OFFSET" sheetId="7" r:id="rId7"/>
     <sheet name="OFFSET-1" sheetId="8" r:id="rId8"/>
   </sheets>
+  <definedNames>
+    <definedName name="Diameter">HLOOKUP!$B$18:$J$21</definedName>
+    <definedName name="planetall">HLOOKUP!$B$18:$B$21</definedName>
+    <definedName name="Temp">'HLOOKUP another sheet'!$A$1:$I$3</definedName>
+  </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
     </ext>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
   </extLst>
 </workbook>
 </file>
 
+<file path=xl/metadata.xml><?xml version="1.0" encoding="utf-8"?>
+<metadata xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xlrd="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata" xmlns:xda="http://schemas.microsoft.com/office/spreadsheetml/2017/dynamicarray">
+  <metadataTypes count="1">
+    <metadataType name="XLDAPR" minSupportedVersion="120000" copy="1" pasteAll="1" pasteValues="1" merge="1" splitFirst="1" rowColShift="1" clearFormats="1" clearComments="1" assign="1" coerce="1" cellMeta="1"/>
+  </metadataTypes>
+  <futureMetadata name="XLDAPR" count="1">
+    <bk>
+      <extLst>
+        <ext uri="{bdbb8cdc-fa1e-496e-a857-3c3f30c029c3}">
+          <xda:dynamicArrayProperties fDynamic="1" fCollapsed="0"/>
+        </ext>
+      </extLst>
+    </bk>
+  </futureMetadata>
+  <cellMetadata count="1">
+    <bk>
+      <rc t="1" v="0"/>
+    </bk>
+  </cellMetadata>
+</metadata>
+</file>
+
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="188" uniqueCount="118">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="191" uniqueCount="118">
   <si>
     <t>Streaming Service</t>
   </si>
@@ -808,11 +846,11 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="5">
-    <numFmt numFmtId="8" formatCode="&quot;₹&quot;\ #,##0.00;[Red]&quot;₹&quot;\ \-#,##0.00"/>
-    <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="164" formatCode="_ [$₹-4009]\ * #,##0.00_ ;_ [$₹-4009]\ * \-#,##0.00_ ;_ [$₹-4009]\ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="165" formatCode="&quot;₹&quot;\ #,##0.00"/>
-    <numFmt numFmtId="166" formatCode="_(* #,##0_);_(* \(#,##0\);_(* &quot;-&quot;??_);_(@_)"/>
+    <numFmt numFmtId="164" formatCode="&quot;₹&quot;\ #,##0.00;[Red]&quot;₹&quot;\ \-#,##0.00"/>
+    <numFmt numFmtId="165" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="166" formatCode="_ [$₹-4009]\ * #,##0.00_ ;_ [$₹-4009]\ * \-#,##0.00_ ;_ [$₹-4009]\ * &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="167" formatCode="&quot;₹&quot;\ #,##0.00"/>
+    <numFmt numFmtId="168" formatCode="_(* #,##0_);_(* \(#,##0\);_(* &quot;-&quot;??_);_(@_)"/>
   </numFmts>
   <fonts count="24" x14ac:knownFonts="1">
     <font>
@@ -1054,9 +1092,9 @@
       <protection locked="0"/>
     </xf>
     <xf numFmtId="0" fontId="20" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="43" fontId="10" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="165" fontId="10" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="46">
+  <cellXfs count="47">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -1078,18 +1116,18 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="166" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
-    <xf numFmtId="165" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="166" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="167" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="165" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
-    <xf numFmtId="8" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="167" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="8" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="18" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -1111,19 +1149,19 @@
     </xf>
     <xf numFmtId="0" fontId="21" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="22" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="166" fontId="23" fillId="0" borderId="0" xfId="5" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="168" fontId="23" fillId="0" borderId="0" xfId="5" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="166" fontId="22" fillId="0" borderId="0" xfId="5" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="168" fontId="22" fillId="0" borderId="0" xfId="5" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="0" fontId="22" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="166" fontId="22" fillId="0" borderId="1" xfId="5" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="166" fontId="22" fillId="2" borderId="1" xfId="5" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="166" fontId="22" fillId="0" borderId="1" xfId="5" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="168" fontId="22" fillId="0" borderId="1" xfId="5" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="168" fontId="22" fillId="2" borderId="1" xfId="5" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="168" fontId="22" fillId="0" borderId="1" xfId="5" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="22" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="3" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="166" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="168" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
@@ -1163,6 +1201,7 @@
     <xf numFmtId="0" fontId="22" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="6">
     <cellStyle name="Comma" xfId="5" builtinId="3"/>
@@ -1255,16 +1294,16 @@
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
-      <xdr:col>3</xdr:col>
-      <xdr:colOff>521805</xdr:colOff>
+      <xdr:col>4</xdr:col>
+      <xdr:colOff>90927</xdr:colOff>
       <xdr:row>23</xdr:row>
-      <xdr:rowOff>18404</xdr:rowOff>
+      <xdr:rowOff>5311</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>13</xdr:col>
-      <xdr:colOff>454164</xdr:colOff>
+      <xdr:col>14</xdr:col>
+      <xdr:colOff>23286</xdr:colOff>
       <xdr:row>27</xdr:row>
-      <xdr:rowOff>24754</xdr:rowOff>
+      <xdr:rowOff>11661</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -1294,8 +1333,8 @@
       </xdr:blipFill>
       <xdr:spPr bwMode="auto">
         <a:xfrm>
-          <a:off x="2879588" y="4308795"/>
-          <a:ext cx="6006272" cy="735220"/>
+          <a:off x="3357734" y="4435010"/>
+          <a:ext cx="6664889" cy="771410"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -1321,16 +1360,16 @@
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
-      <xdr:col>1</xdr:col>
-      <xdr:colOff>598367</xdr:colOff>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
       <xdr:row>5</xdr:row>
-      <xdr:rowOff>5801</xdr:rowOff>
+      <xdr:rowOff>5803</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>11</xdr:col>
-      <xdr:colOff>400540</xdr:colOff>
+      <xdr:col>9</xdr:col>
+      <xdr:colOff>9769</xdr:colOff>
       <xdr:row>8</xdr:row>
-      <xdr:rowOff>12150</xdr:rowOff>
+      <xdr:rowOff>12152</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -1360,8 +1399,8 @@
       </xdr:blipFill>
       <xdr:spPr bwMode="auto">
         <a:xfrm>
-          <a:off x="1614367" y="933878"/>
-          <a:ext cx="5907942" cy="563195"/>
+          <a:off x="0" y="982726"/>
+          <a:ext cx="6604000" cy="592503"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -1710,12 +1749,37 @@
 </a:theme>
 </file>
 
+<file path=xl/webextensions/taskpanes.xml><?xml version="1.0" encoding="utf-8"?>
+<wetp:taskpanes xmlns:wetp="http://schemas.microsoft.com/office/webextensions/taskpanes/2010/11">
+  <wetp:taskpane dockstate="right" visibility="0" width="350" row="0">
+    <wetp:webextensionref xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+  </wetp:taskpane>
+</wetp:taskpanes>
+</file>
+
+<file path=xl/webextensions/webextension1.xml><?xml version="1.0" encoding="utf-8"?>
+<we:webextension xmlns:we="http://schemas.microsoft.com/office/webextensions/webextension/2010/11" id="{69665BD0-D720-EF4E-BACF-6CF0FBBC7132}">
+  <we:reference id="wa200010215" version="2.0.0.0" store="en-GB" storeType="OMEX"/>
+  <we:alternateReferences>
+    <we:reference id="WA200010215" version="2.0.0.0" store="" storeType="OMEX"/>
+  </we:alternateReferences>
+  <we:properties/>
+  <we:bindings/>
+  <we:snapshot xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships"/>
+  <we:extLst>
+    <a:ext xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" uri="{D87F86FE-615C-45B5-9D79-34F1136793EB}">
+      <we:containsCustomFunctions/>
+    </a:ext>
+  </we:extLst>
+</we:webextension>
+</file>
+
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{089B6956-344E-4245-A93A-4F6D104B46EA}">
   <dimension ref="A1:P30"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <sheetData>
-    <row r="1" spans="1:16" ht="21" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:16" ht="21" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1" s="36" t="s">
         <v>12</v>
       </c>
@@ -1735,7 +1799,7 @@
       <c r="O1" s="36"/>
       <c r="P1" s="36"/>
     </row>
-    <row r="2" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A2" s="36"/>
       <c r="B2" s="36"/>
       <c r="C2" s="36"/>
@@ -1753,14 +1817,14 @@
       <c r="O2" s="36"/>
       <c r="P2" s="36"/>
     </row>
-    <row r="3" spans="1:16" ht="20" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:16" ht="16" x14ac:dyDescent="0.2">
       <c r="A3" s="34" t="s">
         <v>30</v>
       </c>
       <c r="B3" s="34"/>
       <c r="C3" s="34"/>
     </row>
-    <row r="4" spans="1:16" ht="17" x14ac:dyDescent="0.5">
+    <row r="4" spans="1:16" ht="17" x14ac:dyDescent="0.25">
       <c r="A4" s="35" t="s">
         <v>13</v>
       </c>
@@ -1769,7 +1833,7 @@
       <c r="D4" s="35"/>
       <c r="E4" s="35"/>
     </row>
-    <row r="6" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A6" s="33" t="s">
         <v>14</v>
       </c>
@@ -1785,7 +1849,7 @@
       <c r="K6" s="33"/>
       <c r="L6" s="33"/>
     </row>
-    <row r="7" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A7" s="33" t="s">
         <v>15</v>
       </c>
@@ -1801,7 +1865,7 @@
       <c r="K7" s="33"/>
       <c r="L7" s="33"/>
     </row>
-    <row r="8" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A8" s="33" t="s">
         <v>16</v>
       </c>
@@ -1817,14 +1881,14 @@
       <c r="K8" s="33"/>
       <c r="L8" s="33"/>
     </row>
-    <row r="10" spans="1:16" ht="20" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:16" ht="16" x14ac:dyDescent="0.2">
       <c r="A10" s="34" t="s">
         <v>31</v>
       </c>
       <c r="B10" s="34"/>
       <c r="C10" s="34"/>
     </row>
-    <row r="11" spans="1:16" ht="17" x14ac:dyDescent="0.5">
+    <row r="11" spans="1:16" ht="17" x14ac:dyDescent="0.25">
       <c r="A11" s="35" t="s">
         <v>32</v>
       </c>
@@ -1837,37 +1901,37 @@
       <c r="H11" s="35"/>
       <c r="I11" s="35"/>
     </row>
-    <row r="13" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A13" t="s">
         <v>35</v>
       </c>
     </row>
-    <row r="15" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="15" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A15" t="s">
         <v>33</v>
       </c>
     </row>
-    <row r="17" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="17" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A17" t="s">
         <v>34</v>
       </c>
     </row>
-    <row r="19" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="19" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A19" t="s">
         <v>36</v>
       </c>
     </row>
-    <row r="20" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="20" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A20" t="s">
         <v>37</v>
       </c>
     </row>
-    <row r="21" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="21" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A21" t="s">
         <v>38</v>
       </c>
     </row>
-    <row r="24" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="24" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A24" s="1" t="s">
         <v>17</v>
       </c>
@@ -1890,7 +1954,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="25" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="25" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A25" s="5" t="s">
         <v>22</v>
       </c>
@@ -1913,7 +1977,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="26" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="26" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A26" s="5" t="s">
         <v>23</v>
       </c>
@@ -1932,9 +1996,12 @@
       <c r="G26" s="4" t="s">
         <v>27</v>
       </c>
-      <c r="H26" s="3"/>
-    </row>
-    <row r="27" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="H26" s="3" t="str" cm="1">
+        <f t="array" ref="H26">INDEX(A24:E30,H24,H25)</f>
+        <v>Paint</v>
+      </c>
+    </row>
+    <row r="27" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A27" s="5" t="s">
         <v>24</v>
       </c>
@@ -1951,7 +2018,7 @@
         <v>54</v>
       </c>
     </row>
-    <row r="28" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="28" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A28" s="5" t="s">
         <v>25</v>
       </c>
@@ -1968,7 +2035,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="29" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="29" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A29" s="5" t="s">
         <v>28</v>
       </c>
@@ -1985,7 +2052,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="30" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="30" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A30" s="5" t="s">
         <v>29</v>
       </c>
@@ -2021,12 +2088,12 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{91FCE7C7-9DAD-449D-9E97-50573B03ED0C}">
   <dimension ref="A1:R35"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="6" max="6" width="14.26953125" customWidth="1"/>
+    <col min="6" max="6" width="14.33203125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:18" ht="21" x14ac:dyDescent="0.5">
+    <row r="1" spans="1:18" ht="21" x14ac:dyDescent="0.25">
       <c r="A1" s="37" t="s">
         <v>39</v>
       </c>
@@ -2048,7 +2115,7 @@
       <c r="Q1" s="37"/>
       <c r="R1" s="37"/>
     </row>
-    <row r="3" spans="1:18" ht="15.5" x14ac:dyDescent="0.45">
+    <row r="3" spans="1:18" ht="16" x14ac:dyDescent="0.25">
       <c r="A3" s="38" t="s">
         <v>40</v>
       </c>
@@ -2058,37 +2125,37 @@
       <c r="E3" s="38"/>
       <c r="F3" s="38"/>
     </row>
-    <row r="5" spans="1:18" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A5" t="s">
         <v>44</v>
       </c>
     </row>
-    <row r="7" spans="1:18" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A7" t="s">
         <v>45</v>
       </c>
     </row>
-    <row r="9" spans="1:18" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A9" t="s">
         <v>46</v>
       </c>
     </row>
-    <row r="11" spans="1:18" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A11" t="s">
         <v>41</v>
       </c>
     </row>
-    <row r="12" spans="1:18" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A12" t="s">
         <v>42</v>
       </c>
     </row>
-    <row r="13" spans="1:18" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A13" t="s">
         <v>43</v>
       </c>
     </row>
-    <row r="16" spans="1:18" x14ac:dyDescent="0.35">
+    <row r="16" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A16" s="1" t="s">
         <v>17</v>
       </c>
@@ -2114,7 +2181,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="17" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="17" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A17" s="5" t="s">
         <v>22</v>
       </c>
@@ -2142,7 +2209,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="18" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="18" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A18" s="5" t="s">
         <v>23</v>
       </c>
@@ -2163,7 +2230,7 @@
         <v>139</v>
       </c>
     </row>
-    <row r="19" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="19" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A19" s="5" t="s">
         <v>24</v>
       </c>
@@ -2184,7 +2251,7 @@
         <v>193</v>
       </c>
     </row>
-    <row r="20" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="20" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A20" s="5" t="s">
         <v>25</v>
       </c>
@@ -2205,7 +2272,7 @@
         <v>191</v>
       </c>
     </row>
-    <row r="21" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="21" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A21" s="5" t="s">
         <v>28</v>
       </c>
@@ -2226,7 +2293,7 @@
         <v>175</v>
       </c>
     </row>
-    <row r="22" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="22" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A22" s="5" t="s">
         <v>29</v>
       </c>
@@ -2247,7 +2314,7 @@
         <v>171</v>
       </c>
     </row>
-    <row r="25" spans="1:9" ht="18.5" x14ac:dyDescent="0.45">
+    <row r="25" spans="1:9" ht="19" x14ac:dyDescent="0.25">
       <c r="A25" s="39" t="s">
         <v>49</v>
       </c>
@@ -2256,7 +2323,7 @@
       <c r="D25" s="39"/>
       <c r="E25" s="39"/>
     </row>
-    <row r="27" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="27" spans="1:9" x14ac:dyDescent="0.2">
       <c r="B27" s="7" t="s">
         <v>17</v>
       </c>
@@ -2264,7 +2331,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="28" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="28" spans="1:9" x14ac:dyDescent="0.2">
       <c r="B28" s="7" t="s">
         <v>26</v>
       </c>
@@ -2272,13 +2339,13 @@
         <v>21</v>
       </c>
     </row>
-    <row r="29" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="29" spans="1:9" x14ac:dyDescent="0.2">
       <c r="B29" s="7" t="s">
         <v>11</v>
       </c>
       <c r="C29" s="8"/>
     </row>
-    <row r="31" spans="1:9" ht="18.5" x14ac:dyDescent="0.45">
+    <row r="31" spans="1:9" ht="19" x14ac:dyDescent="0.25">
       <c r="A31" s="39" t="s">
         <v>51</v>
       </c>
@@ -2287,7 +2354,7 @@
       <c r="D31" s="39"/>
       <c r="E31" s="39"/>
     </row>
-    <row r="33" spans="2:3" x14ac:dyDescent="0.35">
+    <row r="33" spans="2:3" x14ac:dyDescent="0.2">
       <c r="B33" s="7" t="s">
         <v>17</v>
       </c>
@@ -2295,13 +2362,13 @@
         <v>29</v>
       </c>
     </row>
-    <row r="34" spans="2:3" x14ac:dyDescent="0.35">
+    <row r="34" spans="2:3" x14ac:dyDescent="0.2">
       <c r="B34" s="7" t="s">
         <v>26</v>
       </c>
       <c r="C34" s="2"/>
     </row>
-    <row r="35" spans="2:3" x14ac:dyDescent="0.35">
+    <row r="35" spans="2:3" x14ac:dyDescent="0.2">
       <c r="B35" s="7" t="s">
         <v>11</v>
       </c>
@@ -2329,14 +2396,14 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="B2:G12"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="2" max="2" width="15.54296875" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="10.08984375" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="8.26953125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="15.5" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="10.1640625" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="8.33203125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="2:7" x14ac:dyDescent="0.35">
+    <row r="2" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B2" s="40" t="s">
         <v>52</v>
       </c>
@@ -2345,7 +2412,7 @@
       <c r="E2" s="40"/>
       <c r="F2" s="40"/>
     </row>
-    <row r="4" spans="2:7" x14ac:dyDescent="0.35">
+    <row r="4" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B4" s="1" t="s">
         <v>0</v>
       </c>
@@ -2365,7 +2432,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="5" spans="2:7" x14ac:dyDescent="0.35">
+    <row r="5" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B5" s="2" t="s">
         <v>5</v>
       </c>
@@ -2386,7 +2453,7 @@
         <v>4.7900000000000009</v>
       </c>
     </row>
-    <row r="6" spans="2:7" x14ac:dyDescent="0.35">
+    <row r="6" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B6" s="2" t="s">
         <v>6</v>
       </c>
@@ -2407,7 +2474,7 @@
         <v>29.64</v>
       </c>
     </row>
-    <row r="7" spans="2:7" x14ac:dyDescent="0.35">
+    <row r="7" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B7" s="2" t="s">
         <v>7</v>
       </c>
@@ -2428,7 +2495,7 @@
         <v>4.7</v>
       </c>
     </row>
-    <row r="8" spans="2:7" x14ac:dyDescent="0.35">
+    <row r="8" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B8" s="2" t="s">
         <v>8</v>
       </c>
@@ -2449,7 +2516,7 @@
         <v>39.130000000000003</v>
       </c>
     </row>
-    <row r="10" spans="2:7" x14ac:dyDescent="0.35">
+    <row r="10" spans="2:7" x14ac:dyDescent="0.2">
       <c r="C10" s="3" t="s">
         <v>9</v>
       </c>
@@ -2457,7 +2524,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="11" spans="2:7" x14ac:dyDescent="0.35">
+    <row r="11" spans="2:7" x14ac:dyDescent="0.2">
       <c r="C11" s="3" t="s">
         <v>10</v>
       </c>
@@ -2465,7 +2532,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="12" spans="2:7" x14ac:dyDescent="0.35">
+    <row r="12" spans="2:7" x14ac:dyDescent="0.2">
       <c r="C12" s="3" t="s">
         <v>11</v>
       </c>
@@ -2482,15 +2549,15 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2A22B175-A37F-4265-9C45-B198556BE1F7}">
   <dimension ref="B2:Q35"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="3" max="3" width="10.1796875" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="11.453125" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="10.90625" customWidth="1"/>
-    <col min="8" max="8" width="11.1796875" customWidth="1"/>
+    <col min="3" max="3" width="10.1640625" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="11.5" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="10.83203125" customWidth="1"/>
+    <col min="8" max="8" width="11.1640625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="2:17" x14ac:dyDescent="0.35">
+    <row r="2" spans="2:17" x14ac:dyDescent="0.2">
       <c r="B2" s="41" t="s">
         <v>107</v>
       </c>
@@ -2510,7 +2577,7 @@
       <c r="P2" s="41"/>
       <c r="Q2" s="41"/>
     </row>
-    <row r="3" spans="2:17" x14ac:dyDescent="0.35">
+    <row r="3" spans="2:17" x14ac:dyDescent="0.2">
       <c r="B3" s="41"/>
       <c r="C3" s="41"/>
       <c r="D3" s="41"/>
@@ -2528,7 +2595,7 @@
       <c r="P3" s="41"/>
       <c r="Q3" s="41"/>
     </row>
-    <row r="4" spans="2:17" x14ac:dyDescent="0.35">
+    <row r="4" spans="2:17" x14ac:dyDescent="0.2">
       <c r="B4" s="41"/>
       <c r="C4" s="41"/>
       <c r="D4" s="41"/>
@@ -2546,7 +2613,7 @@
       <c r="P4" s="41"/>
       <c r="Q4" s="41"/>
     </row>
-    <row r="5" spans="2:17" x14ac:dyDescent="0.35">
+    <row r="5" spans="2:17" x14ac:dyDescent="0.2">
       <c r="B5" s="41"/>
       <c r="C5" s="41"/>
       <c r="D5" s="41"/>
@@ -2564,7 +2631,7 @@
       <c r="P5" s="41"/>
       <c r="Q5" s="41"/>
     </row>
-    <row r="7" spans="2:17" x14ac:dyDescent="0.35">
+    <row r="7" spans="2:17" x14ac:dyDescent="0.2">
       <c r="B7" s="42" t="s">
         <v>53</v>
       </c>
@@ -2584,7 +2651,7 @@
       <c r="P7" s="42"/>
       <c r="Q7" s="42"/>
     </row>
-    <row r="8" spans="2:17" x14ac:dyDescent="0.35">
+    <row r="8" spans="2:17" x14ac:dyDescent="0.2">
       <c r="B8" s="42"/>
       <c r="C8" s="42"/>
       <c r="D8" s="42"/>
@@ -2602,7 +2669,7 @@
       <c r="P8" s="42"/>
       <c r="Q8" s="42"/>
     </row>
-    <row r="9" spans="2:17" x14ac:dyDescent="0.35">
+    <row r="9" spans="2:17" x14ac:dyDescent="0.2">
       <c r="B9" s="42"/>
       <c r="C9" s="42"/>
       <c r="D9" s="42"/>
@@ -2620,7 +2687,7 @@
       <c r="P9" s="42"/>
       <c r="Q9" s="42"/>
     </row>
-    <row r="11" spans="2:17" ht="20" x14ac:dyDescent="0.35">
+    <row r="11" spans="2:17" ht="16" x14ac:dyDescent="0.2">
       <c r="B11" s="43" t="s">
         <v>54</v>
       </c>
@@ -2637,47 +2704,47 @@
       <c r="L11" s="44"/>
       <c r="M11" s="44"/>
     </row>
-    <row r="13" spans="2:17" x14ac:dyDescent="0.35">
+    <row r="13" spans="2:17" x14ac:dyDescent="0.2">
       <c r="B13" t="s">
         <v>56</v>
       </c>
     </row>
-    <row r="15" spans="2:17" x14ac:dyDescent="0.35">
+    <row r="15" spans="2:17" x14ac:dyDescent="0.2">
       <c r="B15" t="s">
         <v>59</v>
       </c>
     </row>
-    <row r="16" spans="2:17" x14ac:dyDescent="0.35">
+    <row r="16" spans="2:17" x14ac:dyDescent="0.2">
       <c r="B16" t="s">
         <v>57</v>
       </c>
     </row>
-    <row r="18" spans="2:8" x14ac:dyDescent="0.35">
+    <row r="18" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B18" t="s">
         <v>60</v>
       </c>
     </row>
-    <row r="19" spans="2:8" x14ac:dyDescent="0.35">
+    <row r="19" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B19" t="s">
         <v>58</v>
       </c>
     </row>
-    <row r="20" spans="2:8" x14ac:dyDescent="0.35">
+    <row r="20" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B20" t="s">
         <v>61</v>
       </c>
     </row>
-    <row r="21" spans="2:8" x14ac:dyDescent="0.35">
+    <row r="21" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B21" t="s">
         <v>62</v>
       </c>
     </row>
-    <row r="22" spans="2:8" x14ac:dyDescent="0.35">
+    <row r="22" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B22" t="s">
         <v>63</v>
       </c>
     </row>
-    <row r="24" spans="2:8" x14ac:dyDescent="0.35">
+    <row r="24" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B24" s="15" t="s">
         <v>64</v>
       </c>
@@ -2688,7 +2755,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="25" spans="2:8" x14ac:dyDescent="0.35">
+    <row r="25" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B25" s="2">
         <v>1</v>
       </c>
@@ -2708,7 +2775,7 @@
         <v>77</v>
       </c>
     </row>
-    <row r="26" spans="2:8" x14ac:dyDescent="0.35">
+    <row r="26" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B26" s="2">
         <v>2</v>
       </c>
@@ -2724,7 +2791,7 @@
       <c r="G26" s="3"/>
       <c r="H26" s="3"/>
     </row>
-    <row r="27" spans="2:8" x14ac:dyDescent="0.35">
+    <row r="27" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B27" s="2">
         <v>3</v>
       </c>
@@ -2740,7 +2807,7 @@
       <c r="G27" s="3"/>
       <c r="H27" s="3"/>
     </row>
-    <row r="28" spans="2:8" x14ac:dyDescent="0.35">
+    <row r="28" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B28" s="2">
         <v>4</v>
       </c>
@@ -2756,7 +2823,7 @@
       <c r="G28" s="3"/>
       <c r="H28" s="3"/>
     </row>
-    <row r="29" spans="2:8" x14ac:dyDescent="0.35">
+    <row r="29" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B29" s="2">
         <v>5</v>
       </c>
@@ -2772,7 +2839,7 @@
       <c r="G29" s="3"/>
       <c r="H29" s="3"/>
     </row>
-    <row r="30" spans="2:8" x14ac:dyDescent="0.35">
+    <row r="30" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B30" s="2">
         <v>6</v>
       </c>
@@ -2783,7 +2850,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="31" spans="2:8" x14ac:dyDescent="0.35">
+    <row r="31" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B31" s="2">
         <v>7</v>
       </c>
@@ -2794,7 +2861,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="32" spans="2:8" x14ac:dyDescent="0.35">
+    <row r="32" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B32" s="2">
         <v>8</v>
       </c>
@@ -2805,7 +2872,7 @@
         <v>39.35</v>
       </c>
     </row>
-    <row r="33" spans="2:4" x14ac:dyDescent="0.35">
+    <row r="33" spans="2:4" x14ac:dyDescent="0.2">
       <c r="B33" s="2">
         <v>9</v>
       </c>
@@ -2816,7 +2883,7 @@
         <v>35.5</v>
       </c>
     </row>
-    <row r="34" spans="2:4" x14ac:dyDescent="0.35">
+    <row r="34" spans="2:4" x14ac:dyDescent="0.2">
       <c r="B34" s="2">
         <v>10</v>
       </c>
@@ -2827,7 +2894,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="35" spans="2:4" x14ac:dyDescent="0.35">
+    <row r="35" spans="2:4" x14ac:dyDescent="0.2">
       <c r="C35" s="16"/>
     </row>
   </sheetData>
@@ -2850,12 +2917,12 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3AF69163-8ED4-4508-B550-88F17167F9B1}">
   <dimension ref="B2:Q26"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="2" max="2" width="16.36328125" customWidth="1"/>
+    <col min="2" max="2" width="16.33203125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="2:17" x14ac:dyDescent="0.35">
+    <row r="2" spans="2:17" x14ac:dyDescent="0.2">
       <c r="B2" s="41" t="s">
         <v>108</v>
       </c>
@@ -2875,7 +2942,7 @@
       <c r="P2" s="41"/>
       <c r="Q2" s="41"/>
     </row>
-    <row r="3" spans="2:17" x14ac:dyDescent="0.35">
+    <row r="3" spans="2:17" x14ac:dyDescent="0.2">
       <c r="B3" s="41"/>
       <c r="C3" s="41"/>
       <c r="D3" s="41"/>
@@ -2893,7 +2960,7 @@
       <c r="P3" s="41"/>
       <c r="Q3" s="41"/>
     </row>
-    <row r="4" spans="2:17" x14ac:dyDescent="0.35">
+    <row r="4" spans="2:17" x14ac:dyDescent="0.2">
       <c r="B4" s="41"/>
       <c r="C4" s="41"/>
       <c r="D4" s="41"/>
@@ -2911,7 +2978,7 @@
       <c r="P4" s="41"/>
       <c r="Q4" s="41"/>
     </row>
-    <row r="6" spans="2:17" ht="20" x14ac:dyDescent="0.35">
+    <row r="6" spans="2:17" ht="16" x14ac:dyDescent="0.2">
       <c r="B6" s="43" t="s">
         <v>78</v>
       </c>
@@ -2928,41 +2995,41 @@
       <c r="L6" s="44"/>
       <c r="M6" s="44"/>
     </row>
-    <row r="7" spans="2:17" ht="16.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="7" spans="2:17" ht="16.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B7" s="17"/>
       <c r="C7" s="17"/>
     </row>
-    <row r="8" spans="2:17" x14ac:dyDescent="0.35">
+    <row r="8" spans="2:17" x14ac:dyDescent="0.2">
       <c r="B8" t="s">
         <v>81</v>
       </c>
     </row>
-    <row r="9" spans="2:17" x14ac:dyDescent="0.35">
+    <row r="9" spans="2:17" x14ac:dyDescent="0.2">
       <c r="B9" t="s">
         <v>82</v>
       </c>
     </row>
-    <row r="10" spans="2:17" x14ac:dyDescent="0.35">
+    <row r="10" spans="2:17" x14ac:dyDescent="0.2">
       <c r="B10" t="s">
         <v>83</v>
       </c>
     </row>
-    <row r="11" spans="2:17" x14ac:dyDescent="0.35">
+    <row r="11" spans="2:17" x14ac:dyDescent="0.2">
       <c r="B11" t="s">
         <v>80</v>
       </c>
     </row>
-    <row r="13" spans="2:17" x14ac:dyDescent="0.35">
+    <row r="13" spans="2:17" x14ac:dyDescent="0.2">
       <c r="B13" t="s">
         <v>84</v>
       </c>
     </row>
-    <row r="15" spans="2:17" x14ac:dyDescent="0.35">
+    <row r="15" spans="2:17" x14ac:dyDescent="0.2">
       <c r="B15" t="s">
         <v>85</v>
       </c>
     </row>
-    <row r="18" spans="2:10" x14ac:dyDescent="0.35">
+    <row r="18" spans="2:10" x14ac:dyDescent="0.2">
       <c r="B18" s="18" t="s">
         <v>86</v>
       </c>
@@ -2991,7 +3058,7 @@
         <v>94</v>
       </c>
     </row>
-    <row r="19" spans="2:10" x14ac:dyDescent="0.35">
+    <row r="19" spans="2:10" x14ac:dyDescent="0.2">
       <c r="B19" s="18" t="s">
         <v>95</v>
       </c>
@@ -3020,7 +3087,7 @@
         <v>49528</v>
       </c>
     </row>
-    <row r="20" spans="2:10" x14ac:dyDescent="0.35">
+    <row r="20" spans="2:10" x14ac:dyDescent="0.2">
       <c r="B20" s="18" t="s">
         <v>109</v>
       </c>
@@ -3049,44 +3116,77 @@
         <v>888</v>
       </c>
     </row>
-    <row r="21" spans="2:10" x14ac:dyDescent="0.35">
+    <row r="21" spans="2:10" x14ac:dyDescent="0.2">
       <c r="B21" s="18" t="s">
         <v>110</v>
       </c>
-      <c r="C21" s="3"/>
-      <c r="D21" s="3"/>
-      <c r="E21" s="3"/>
-      <c r="F21" s="3"/>
-      <c r="G21" s="3"/>
-      <c r="H21" s="3"/>
-      <c r="I21" s="3"/>
-      <c r="J21" s="3"/>
-    </row>
-    <row r="23" spans="2:10" x14ac:dyDescent="0.35">
+      <c r="C21" s="3">
+        <f>HLOOKUP(HLOOKUP!C18,Temp,2,FALSE)</f>
+        <v>59</v>
+      </c>
+      <c r="D21" s="3">
+        <f>HLOOKUP(HLOOKUP!D18,Temp,2,FALSE)</f>
+        <v>-9.4</v>
+      </c>
+      <c r="E21" s="3">
+        <f>HLOOKUP(HLOOKUP!E18,Temp,2,FALSE)</f>
+        <v>468</v>
+      </c>
+      <c r="F21" s="3">
+        <f>HLOOKUP(HLOOKUP!F18,Temp,2,FALSE)</f>
+        <v>869</v>
+      </c>
+      <c r="G21" s="3">
+        <f>HLOOKUP(HLOOKUP!G18,Temp,2,FALSE)</f>
+        <v>-238</v>
+      </c>
+      <c r="H21" s="3">
+        <f>HLOOKUP(HLOOKUP!H18,Temp,2,FALSE)</f>
+        <v>-292</v>
+      </c>
+      <c r="I21" s="3">
+        <f>HLOOKUP(HLOOKUP!I18,Temp,2,FALSE)</f>
+        <v>-357</v>
+      </c>
+      <c r="J21" s="3">
+        <f>HLOOKUP(HLOOKUP!J18,Temp,2,FALSE)</f>
+        <v>-346</v>
+      </c>
+    </row>
+    <row r="23" spans="2:10" x14ac:dyDescent="0.2">
       <c r="B23" s="4" t="s">
         <v>86</v>
       </c>
       <c r="C23" s="3" t="s">
-        <v>94</v>
-      </c>
-    </row>
-    <row r="24" spans="2:10" x14ac:dyDescent="0.35">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="24" spans="2:10" x14ac:dyDescent="0.2">
       <c r="B24" s="4" t="s">
         <v>95</v>
       </c>
-      <c r="C24" s="3"/>
-    </row>
-    <row r="25" spans="2:10" x14ac:dyDescent="0.35">
+      <c r="C24" s="3">
+        <f>HLOOKUP($C$23,$B$18:$J$21,MATCH(B24,$B$18:$B$21,0),FALSE)</f>
+        <v>4878</v>
+      </c>
+    </row>
+    <row r="25" spans="2:10" x14ac:dyDescent="0.2">
       <c r="B25" s="4" t="s">
         <v>109</v>
       </c>
-      <c r="C25" s="3"/>
-    </row>
-    <row r="26" spans="2:10" x14ac:dyDescent="0.35">
+      <c r="C25" s="3">
+        <f>HLOOKUP($C$23,$B$18:$J$21,MATCH(B25,$B$18:$B$21,0),FALSE)</f>
+        <v>333</v>
+      </c>
+    </row>
+    <row r="26" spans="2:10" x14ac:dyDescent="0.2">
       <c r="B26" s="4" t="s">
         <v>110</v>
       </c>
-      <c r="C26" s="3"/>
+      <c r="C26" s="3">
+        <f>HLOOKUP($C$23,$B$18:$J$21,MATCH(B26,$B$18:$B$21,0),FALSE)</f>
+        <v>468</v>
+      </c>
     </row>
   </sheetData>
   <dataConsolidate/>
@@ -3107,13 +3207,14 @@
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B6DEBD0C-7074-415E-8082-546D486D951D}">
-  <dimension ref="A1:I3"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <dimension ref="A1:I13"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="14.54296875" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="14.5" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="10.1640625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A1" s="18" t="s">
         <v>86</v>
       </c>
@@ -3142,7 +3243,7 @@
         <v>94</v>
       </c>
     </row>
-    <row r="2" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A2" s="18" t="s">
         <v>110</v>
       </c>
@@ -3171,18 +3272,55 @@
         <v>-346</v>
       </c>
     </row>
-    <row r="3" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A3" s="18" t="s">
         <v>95</v>
       </c>
-      <c r="B3" s="31"/>
-      <c r="C3" s="31"/>
-      <c r="D3" s="31"/>
-      <c r="E3" s="31"/>
-      <c r="F3" s="31"/>
-      <c r="G3" s="31"/>
-      <c r="H3" s="31"/>
-      <c r="I3" s="31"/>
+      <c r="B3" s="31">
+        <f>HLOOKUP(B1,Diameter,MATCH($A$3,planetall,0),FALSE)</f>
+        <v>4878</v>
+      </c>
+      <c r="C3" s="31">
+        <f>HLOOKUP(C1,Diameter,MATCH($A$3,planetall,0),FALSE)</f>
+        <v>12104</v>
+      </c>
+      <c r="D3" s="31">
+        <f>HLOOKUP(D1,Diameter,MATCH($A$3,planetall,0),FALSE)</f>
+        <v>12755</v>
+      </c>
+      <c r="E3" s="31">
+        <f>HLOOKUP(E1,Diameter,MATCH($A$3,planetall,0),FALSE)</f>
+        <v>6790</v>
+      </c>
+      <c r="F3" s="31">
+        <f>HLOOKUP(F1,Diameter,MATCH($A$3,planetall,0),FALSE)</f>
+        <v>142796</v>
+      </c>
+      <c r="G3" s="31">
+        <f>HLOOKUP(G1,Diameter,MATCH($A$3,planetall,0),FALSE)</f>
+        <v>120660</v>
+      </c>
+      <c r="H3" s="31">
+        <f>HLOOKUP(H1,Diameter,MATCH($A$3,planetall,0),FALSE)</f>
+        <v>51118</v>
+      </c>
+      <c r="I3" s="31">
+        <f>HLOOKUP(I1,Diameter,MATCH(H3,HLOOKUP!I18:I21,0),FALSE)</f>
+        <v>49528</v>
+      </c>
+    </row>
+    <row r="12" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="B12" s="46" t="s">
+        <v>86</v>
+      </c>
+      <c r="C12" t="s">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="13" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="B13" s="46" t="s">
+        <v>95</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -3193,13 +3331,13 @@
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B122B458-3801-4A6D-9422-25DE16CA3CEF}">
   <dimension ref="B3:I23"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="2" max="2" width="15.90625" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="11.7265625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="15.83203125" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="11.6640625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="3" spans="2:9" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="3" spans="2:9" ht="16" x14ac:dyDescent="0.2">
       <c r="B3" s="21" t="s">
         <v>96</v>
       </c>
@@ -3209,7 +3347,7 @@
       <c r="F3" s="22"/>
       <c r="G3" s="22"/>
     </row>
-    <row r="4" spans="2:9" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="4" spans="2:9" ht="16" x14ac:dyDescent="0.2">
       <c r="B4" s="23"/>
       <c r="C4" s="23"/>
       <c r="D4" s="23"/>
@@ -3217,7 +3355,7 @@
       <c r="F4" s="23"/>
       <c r="G4" s="23"/>
     </row>
-    <row r="5" spans="2:9" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="5" spans="2:9" ht="16" x14ac:dyDescent="0.2">
       <c r="B5" s="23" t="s">
         <v>97</v>
       </c>
@@ -3229,7 +3367,7 @@
       <c r="F5" s="25"/>
       <c r="G5" s="25"/>
     </row>
-    <row r="6" spans="2:9" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="6" spans="2:9" ht="16" x14ac:dyDescent="0.2">
       <c r="B6" s="23"/>
       <c r="C6" s="23"/>
       <c r="D6" s="23"/>
@@ -3238,7 +3376,7 @@
       <c r="G6" s="23"/>
       <c r="I6" s="32"/>
     </row>
-    <row r="7" spans="2:9" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="7" spans="2:9" ht="16" x14ac:dyDescent="0.2">
       <c r="B7" s="26" t="s">
         <v>98</v>
       </c>
@@ -3258,7 +3396,7 @@
         <v>99</v>
       </c>
     </row>
-    <row r="8" spans="2:9" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="8" spans="2:9" ht="16" x14ac:dyDescent="0.2">
       <c r="B8" s="26" t="s">
         <v>100</v>
       </c>
@@ -3279,7 +3417,7 @@
       </c>
       <c r="I8" s="32"/>
     </row>
-    <row r="9" spans="2:9" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="9" spans="2:9" ht="16" x14ac:dyDescent="0.2">
       <c r="B9" s="26" t="s">
         <v>101</v>
       </c>
@@ -3299,7 +3437,7 @@
         <v>3000</v>
       </c>
     </row>
-    <row r="10" spans="2:9" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="10" spans="2:9" ht="16" x14ac:dyDescent="0.2">
       <c r="B10" s="26" t="s">
         <v>102</v>
       </c>
@@ -3319,7 +3457,7 @@
         <v>400</v>
       </c>
     </row>
-    <row r="11" spans="2:9" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="11" spans="2:9" ht="16" x14ac:dyDescent="0.2">
       <c r="B11" s="26" t="s">
         <v>103</v>
       </c>
@@ -3339,7 +3477,7 @@
         <v>2500</v>
       </c>
     </row>
-    <row r="12" spans="2:9" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="12" spans="2:9" ht="16" x14ac:dyDescent="0.2">
       <c r="B12" s="26" t="s">
         <v>104</v>
       </c>
@@ -3359,7 +3497,7 @@
         <v>500</v>
       </c>
     </row>
-    <row r="15" spans="2:9" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="15" spans="2:9" ht="16" x14ac:dyDescent="0.2">
       <c r="B15" s="26" t="s">
         <v>98</v>
       </c>
@@ -3379,7 +3517,7 @@
         <v>99</v>
       </c>
     </row>
-    <row r="16" spans="2:9" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="16" spans="2:9" ht="16" x14ac:dyDescent="0.2">
       <c r="B16" s="26" t="s">
         <v>100</v>
       </c>
@@ -3399,7 +3537,7 @@
         <v>5000</v>
       </c>
     </row>
-    <row r="17" spans="2:7" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="17" spans="2:7" ht="16" x14ac:dyDescent="0.2">
       <c r="B17" s="26" t="s">
         <v>101</v>
       </c>
@@ -3419,7 +3557,7 @@
         <v>3000</v>
       </c>
     </row>
-    <row r="18" spans="2:7" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="18" spans="2:7" ht="16" x14ac:dyDescent="0.2">
       <c r="B18" s="26" t="s">
         <v>102</v>
       </c>
@@ -3439,7 +3577,7 @@
         <v>400</v>
       </c>
     </row>
-    <row r="19" spans="2:7" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="19" spans="2:7" ht="16" x14ac:dyDescent="0.2">
       <c r="B19" s="26" t="s">
         <v>103</v>
       </c>
@@ -3459,7 +3597,7 @@
         <v>2500</v>
       </c>
     </row>
-    <row r="20" spans="2:7" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="20" spans="2:7" ht="16" x14ac:dyDescent="0.2">
       <c r="B20" s="26" t="s">
         <v>104</v>
       </c>
@@ -3479,7 +3617,7 @@
         <v>500</v>
       </c>
     </row>
-    <row r="21" spans="2:7" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="21" spans="2:7" ht="16" x14ac:dyDescent="0.2">
       <c r="B21" s="23"/>
       <c r="C21" s="23"/>
       <c r="D21" s="23"/>
@@ -3487,7 +3625,7 @@
       <c r="F21" s="23"/>
       <c r="G21" s="23"/>
     </row>
-    <row r="22" spans="2:7" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="22" spans="2:7" ht="16" x14ac:dyDescent="0.2">
       <c r="B22" s="45" t="s">
         <v>106</v>
       </c>
@@ -3500,7 +3638,7 @@
       <c r="F22" s="23"/>
       <c r="G22" s="23"/>
     </row>
-    <row r="23" spans="2:7" x14ac:dyDescent="0.35">
+    <row r="23" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B23" s="45"/>
     </row>
   </sheetData>
@@ -3514,12 +3652,12 @@
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{93DCCC3B-7669-464B-A51B-001D3BF716AA}">
   <dimension ref="B2:I11"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="2" max="2" width="20.1796875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="20.1640625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="2:9" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="2" spans="2:9" ht="16" x14ac:dyDescent="0.2">
       <c r="B2" s="21" t="s">
         <v>96</v>
       </c>
@@ -3532,7 +3670,7 @@
         <v>116</v>
       </c>
     </row>
-    <row r="3" spans="2:9" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="3" spans="2:9" ht="16" x14ac:dyDescent="0.2">
       <c r="B3" s="23"/>
       <c r="C3" s="23" t="s">
         <v>111</v>
@@ -3550,7 +3688,7 @@
         <v>115</v>
       </c>
     </row>
-    <row r="4" spans="2:9" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="4" spans="2:9" ht="16" x14ac:dyDescent="0.2">
       <c r="B4" s="23" t="s">
         <v>105</v>
       </c>
@@ -3560,7 +3698,7 @@
       <c r="F4" s="25"/>
       <c r="G4" s="25"/>
     </row>
-    <row r="5" spans="2:9" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="5" spans="2:9" ht="16" x14ac:dyDescent="0.2">
       <c r="B5" s="23"/>
       <c r="C5" s="23"/>
       <c r="D5" s="23"/>
@@ -3568,7 +3706,7 @@
       <c r="F5" s="23"/>
       <c r="G5" s="23"/>
     </row>
-    <row r="6" spans="2:9" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="6" spans="2:9" ht="16" x14ac:dyDescent="0.2">
       <c r="B6" s="26" t="s">
         <v>98</v>
       </c>
@@ -3588,7 +3726,7 @@
         <v>99</v>
       </c>
     </row>
-    <row r="7" spans="2:9" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="7" spans="2:9" ht="16" x14ac:dyDescent="0.2">
       <c r="B7" s="26" t="s">
         <v>100</v>
       </c>
@@ -3608,7 +3746,7 @@
         <v>5000</v>
       </c>
     </row>
-    <row r="8" spans="2:9" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="8" spans="2:9" ht="16" x14ac:dyDescent="0.2">
       <c r="B8" s="26" t="s">
         <v>101</v>
       </c>
@@ -3628,7 +3766,7 @@
         <v>3000</v>
       </c>
     </row>
-    <row r="9" spans="2:9" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="9" spans="2:9" ht="16" x14ac:dyDescent="0.2">
       <c r="B9" s="26" t="s">
         <v>102</v>
       </c>
@@ -3648,7 +3786,7 @@
         <v>400</v>
       </c>
     </row>
-    <row r="10" spans="2:9" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="10" spans="2:9" ht="16" x14ac:dyDescent="0.2">
       <c r="B10" s="26" t="s">
         <v>103</v>
       </c>
@@ -3668,7 +3806,7 @@
         <v>2500</v>
       </c>
     </row>
-    <row r="11" spans="2:9" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="11" spans="2:9" ht="16" x14ac:dyDescent="0.2">
       <c r="B11" s="26" t="s">
         <v>104</v>
       </c>

--- a/Advexcel/Looking up the value INDEX MATCH - Stu.xlsx
+++ b/Advexcel/Looking up the value INDEX MATCH - Stu.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/karan/Desktop/EXCEL ITVEDANT/Advexcel/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2FCE32CF-70C6-0741-A9D0-D916E5029406}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2038DD6A-9F1F-7D45-BB5C-C4405C357391}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="660" windowWidth="29400" windowHeight="18460" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="660" windowWidth="29400" windowHeight="18460" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="INDEX" sheetId="2" r:id="rId1"/>
@@ -48,7 +48,7 @@
 </file>
 
 <file path=xl/metadata.xml><?xml version="1.0" encoding="utf-8"?>
-<metadata xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xlrd="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata" xmlns:xda="http://schemas.microsoft.com/office/spreadsheetml/2017/dynamicarray">
+<metadata xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xda="http://schemas.microsoft.com/office/spreadsheetml/2017/dynamicarray">
   <metadataTypes count="1">
     <metadataType name="XLDAPR" minSupportedVersion="120000" copy="1" pasteAll="1" pasteValues="1" merge="1" splitFirst="1" rowColShift="1" clearFormats="1" clearComments="1" assign="1" coerce="1" cellMeta="1"/>
   </metadataTypes>
@@ -70,7 +70,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="191" uniqueCount="118">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="193" uniqueCount="120">
   <si>
     <t>Streaming Service</t>
   </si>
@@ -839,6 +839,12 @@
   </si>
   <si>
     <t>Total Sales</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> </t>
+  </si>
+  <si>
+    <t>Monday Sales</t>
   </si>
 </sst>
 </file>
@@ -1094,7 +1100,7 @@
     <xf numFmtId="0" fontId="20" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="165" fontId="10" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="47">
+  <cellXfs count="49">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -1162,6 +1168,16 @@
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="168" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
@@ -1198,10 +1214,6 @@
     <xf numFmtId="0" fontId="16" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="6">
     <cellStyle name="Comma" xfId="5" builtinId="3"/>
@@ -1361,15 +1373,15 @@
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
       <xdr:col>0</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>5</xdr:row>
-      <xdr:rowOff>5803</xdr:rowOff>
+      <xdr:colOff>9769</xdr:colOff>
+      <xdr:row>4</xdr:row>
+      <xdr:rowOff>171881</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>9</xdr:col>
-      <xdr:colOff>9769</xdr:colOff>
-      <xdr:row>8</xdr:row>
-      <xdr:rowOff>12152</xdr:rowOff>
+      <xdr:colOff>19538</xdr:colOff>
+      <xdr:row>7</xdr:row>
+      <xdr:rowOff>178230</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -1399,7 +1411,7 @@
       </xdr:blipFill>
       <xdr:spPr bwMode="auto">
         <a:xfrm>
-          <a:off x="0" y="982726"/>
+          <a:off x="9769" y="953419"/>
           <a:ext cx="6604000" cy="592503"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
@@ -1780,126 +1792,126 @@
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <sheetData>
     <row r="1" spans="1:16" ht="21" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A1" s="36" t="s">
+      <c r="A1" s="40" t="s">
         <v>12</v>
       </c>
-      <c r="B1" s="36"/>
-      <c r="C1" s="36"/>
-      <c r="D1" s="36"/>
-      <c r="E1" s="36"/>
-      <c r="F1" s="36"/>
-      <c r="G1" s="36"/>
-      <c r="H1" s="36"/>
-      <c r="I1" s="36"/>
-      <c r="J1" s="36"/>
-      <c r="K1" s="36"/>
-      <c r="L1" s="36"/>
-      <c r="M1" s="36"/>
-      <c r="N1" s="36"/>
-      <c r="O1" s="36"/>
-      <c r="P1" s="36"/>
+      <c r="B1" s="40"/>
+      <c r="C1" s="40"/>
+      <c r="D1" s="40"/>
+      <c r="E1" s="40"/>
+      <c r="F1" s="40"/>
+      <c r="G1" s="40"/>
+      <c r="H1" s="40"/>
+      <c r="I1" s="40"/>
+      <c r="J1" s="40"/>
+      <c r="K1" s="40"/>
+      <c r="L1" s="40"/>
+      <c r="M1" s="40"/>
+      <c r="N1" s="40"/>
+      <c r="O1" s="40"/>
+      <c r="P1" s="40"/>
     </row>
     <row r="2" spans="1:16" x14ac:dyDescent="0.2">
-      <c r="A2" s="36"/>
-      <c r="B2" s="36"/>
-      <c r="C2" s="36"/>
-      <c r="D2" s="36"/>
-      <c r="E2" s="36"/>
-      <c r="F2" s="36"/>
-      <c r="G2" s="36"/>
-      <c r="H2" s="36"/>
-      <c r="I2" s="36"/>
-      <c r="J2" s="36"/>
-      <c r="K2" s="36"/>
-      <c r="L2" s="36"/>
-      <c r="M2" s="36"/>
-      <c r="N2" s="36"/>
-      <c r="O2" s="36"/>
-      <c r="P2" s="36"/>
-    </row>
-    <row r="3" spans="1:16" ht="16" x14ac:dyDescent="0.2">
-      <c r="A3" s="34" t="s">
+      <c r="A2" s="40"/>
+      <c r="B2" s="40"/>
+      <c r="C2" s="40"/>
+      <c r="D2" s="40"/>
+      <c r="E2" s="40"/>
+      <c r="F2" s="40"/>
+      <c r="G2" s="40"/>
+      <c r="H2" s="40"/>
+      <c r="I2" s="40"/>
+      <c r="J2" s="40"/>
+      <c r="K2" s="40"/>
+      <c r="L2" s="40"/>
+      <c r="M2" s="40"/>
+      <c r="N2" s="40"/>
+      <c r="O2" s="40"/>
+      <c r="P2" s="40"/>
+    </row>
+    <row r="3" spans="1:16" ht="20" x14ac:dyDescent="0.2">
+      <c r="A3" s="38" t="s">
         <v>30</v>
       </c>
-      <c r="B3" s="34"/>
-      <c r="C3" s="34"/>
+      <c r="B3" s="38"/>
+      <c r="C3" s="38"/>
     </row>
     <row r="4" spans="1:16" ht="17" x14ac:dyDescent="0.25">
-      <c r="A4" s="35" t="s">
+      <c r="A4" s="39" t="s">
         <v>13</v>
       </c>
-      <c r="B4" s="35"/>
-      <c r="C4" s="35"/>
-      <c r="D4" s="35"/>
-      <c r="E4" s="35"/>
+      <c r="B4" s="39"/>
+      <c r="C4" s="39"/>
+      <c r="D4" s="39"/>
+      <c r="E4" s="39"/>
     </row>
     <row r="6" spans="1:16" x14ac:dyDescent="0.2">
-      <c r="A6" s="33" t="s">
+      <c r="A6" s="37" t="s">
         <v>14</v>
       </c>
-      <c r="B6" s="33"/>
-      <c r="C6" s="33"/>
-      <c r="D6" s="33"/>
-      <c r="E6" s="33"/>
-      <c r="F6" s="33"/>
-      <c r="G6" s="33"/>
-      <c r="H6" s="33"/>
-      <c r="I6" s="33"/>
-      <c r="J6" s="33"/>
-      <c r="K6" s="33"/>
-      <c r="L6" s="33"/>
+      <c r="B6" s="37"/>
+      <c r="C6" s="37"/>
+      <c r="D6" s="37"/>
+      <c r="E6" s="37"/>
+      <c r="F6" s="37"/>
+      <c r="G6" s="37"/>
+      <c r="H6" s="37"/>
+      <c r="I6" s="37"/>
+      <c r="J6" s="37"/>
+      <c r="K6" s="37"/>
+      <c r="L6" s="37"/>
     </row>
     <row r="7" spans="1:16" x14ac:dyDescent="0.2">
-      <c r="A7" s="33" t="s">
+      <c r="A7" s="37" t="s">
         <v>15</v>
       </c>
-      <c r="B7" s="33"/>
-      <c r="C7" s="33"/>
-      <c r="D7" s="33"/>
-      <c r="E7" s="33"/>
-      <c r="F7" s="33"/>
-      <c r="G7" s="33"/>
-      <c r="H7" s="33"/>
-      <c r="I7" s="33"/>
-      <c r="J7" s="33"/>
-      <c r="K7" s="33"/>
-      <c r="L7" s="33"/>
+      <c r="B7" s="37"/>
+      <c r="C7" s="37"/>
+      <c r="D7" s="37"/>
+      <c r="E7" s="37"/>
+      <c r="F7" s="37"/>
+      <c r="G7" s="37"/>
+      <c r="H7" s="37"/>
+      <c r="I7" s="37"/>
+      <c r="J7" s="37"/>
+      <c r="K7" s="37"/>
+      <c r="L7" s="37"/>
     </row>
     <row r="8" spans="1:16" x14ac:dyDescent="0.2">
-      <c r="A8" s="33" t="s">
+      <c r="A8" s="37" t="s">
         <v>16</v>
       </c>
-      <c r="B8" s="33"/>
-      <c r="C8" s="33"/>
-      <c r="D8" s="33"/>
-      <c r="E8" s="33"/>
-      <c r="F8" s="33"/>
-      <c r="G8" s="33"/>
-      <c r="H8" s="33"/>
-      <c r="I8" s="33"/>
-      <c r="J8" s="33"/>
-      <c r="K8" s="33"/>
-      <c r="L8" s="33"/>
-    </row>
-    <row r="10" spans="1:16" ht="16" x14ac:dyDescent="0.2">
-      <c r="A10" s="34" t="s">
+      <c r="B8" s="37"/>
+      <c r="C8" s="37"/>
+      <c r="D8" s="37"/>
+      <c r="E8" s="37"/>
+      <c r="F8" s="37"/>
+      <c r="G8" s="37"/>
+      <c r="H8" s="37"/>
+      <c r="I8" s="37"/>
+      <c r="J8" s="37"/>
+      <c r="K8" s="37"/>
+      <c r="L8" s="37"/>
+    </row>
+    <row r="10" spans="1:16" ht="20" x14ac:dyDescent="0.2">
+      <c r="A10" s="38" t="s">
         <v>31</v>
       </c>
-      <c r="B10" s="34"/>
-      <c r="C10" s="34"/>
+      <c r="B10" s="38"/>
+      <c r="C10" s="38"/>
     </row>
     <row r="11" spans="1:16" ht="17" x14ac:dyDescent="0.25">
-      <c r="A11" s="35" t="s">
+      <c r="A11" s="39" t="s">
         <v>32</v>
       </c>
-      <c r="B11" s="35"/>
-      <c r="C11" s="35"/>
-      <c r="D11" s="35"/>
-      <c r="E11" s="35"/>
-      <c r="F11" s="35"/>
-      <c r="G11" s="35"/>
-      <c r="H11" s="35"/>
-      <c r="I11" s="35"/>
+      <c r="B11" s="39"/>
+      <c r="C11" s="39"/>
+      <c r="D11" s="39"/>
+      <c r="E11" s="39"/>
+      <c r="F11" s="39"/>
+      <c r="G11" s="39"/>
+      <c r="H11" s="39"/>
+      <c r="I11" s="39"/>
     </row>
     <row r="13" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A13" t="s">
@@ -1911,27 +1923,27 @@
         <v>33</v>
       </c>
     </row>
-    <row r="17" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="17" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A17" t="s">
         <v>34</v>
       </c>
     </row>
-    <row r="19" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="19" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A19" t="s">
         <v>36</v>
       </c>
     </row>
-    <row r="20" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="20" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A20" t="s">
         <v>37</v>
       </c>
     </row>
-    <row r="21" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="21" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A21" t="s">
         <v>38</v>
       </c>
     </row>
-    <row r="24" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="24" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A24" s="1" t="s">
         <v>17</v>
       </c>
@@ -1953,8 +1965,11 @@
       <c r="H24" s="3">
         <v>2</v>
       </c>
-    </row>
-    <row r="25" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="J24" s="34"/>
+      <c r="K24" s="33"/>
+      <c r="L24" s="33"/>
+    </row>
+    <row r="25" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A25" s="5" t="s">
         <v>22</v>
       </c>
@@ -1976,8 +1991,10 @@
       <c r="H25" s="3">
         <v>1</v>
       </c>
-    </row>
-    <row r="26" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="J25" s="35"/>
+      <c r="K25" s="33"/>
+    </row>
+    <row r="26" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A26" s="5" t="s">
         <v>23</v>
       </c>
@@ -1997,11 +2014,13 @@
         <v>27</v>
       </c>
       <c r="H26" s="3" t="str" cm="1">
-        <f t="array" ref="H26">INDEX(A24:E30,H24,H25)</f>
-        <v>Paint</v>
-      </c>
-    </row>
-    <row r="27" spans="1:8" x14ac:dyDescent="0.2">
+        <f t="array" ref="H26">INDEX(A25:E30,H24,H25)</f>
+        <v>Brush</v>
+      </c>
+      <c r="J26" s="33"/>
+      <c r="K26" s="33"/>
+    </row>
+    <row r="27" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A27" s="5" t="s">
         <v>24</v>
       </c>
@@ -2017,8 +2036,12 @@
       <c r="E27" s="5">
         <v>54</v>
       </c>
-    </row>
-    <row r="28" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="H27" cm="1">
+        <f t="array" ref="H27">INDEX(B25:E30,H24,H25)</f>
+        <v>23</v>
+      </c>
+    </row>
+    <row r="28" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A28" s="5" t="s">
         <v>25</v>
       </c>
@@ -2035,7 +2058,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="29" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="29" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A29" s="5" t="s">
         <v>28</v>
       </c>
@@ -2052,7 +2075,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="30" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="30" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A30" s="5" t="s">
         <v>29</v>
       </c>
@@ -2094,36 +2117,36 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:18" ht="21" x14ac:dyDescent="0.25">
-      <c r="A1" s="37" t="s">
+      <c r="A1" s="41" t="s">
         <v>39</v>
       </c>
-      <c r="B1" s="37"/>
-      <c r="C1" s="37"/>
-      <c r="D1" s="37"/>
-      <c r="E1" s="37"/>
-      <c r="F1" s="37"/>
-      <c r="G1" s="37"/>
-      <c r="H1" s="37"/>
-      <c r="I1" s="37"/>
-      <c r="J1" s="37"/>
-      <c r="K1" s="37"/>
-      <c r="L1" s="37"/>
-      <c r="M1" s="37"/>
-      <c r="N1" s="37"/>
-      <c r="O1" s="37"/>
-      <c r="P1" s="37"/>
-      <c r="Q1" s="37"/>
-      <c r="R1" s="37"/>
+      <c r="B1" s="41"/>
+      <c r="C1" s="41"/>
+      <c r="D1" s="41"/>
+      <c r="E1" s="41"/>
+      <c r="F1" s="41"/>
+      <c r="G1" s="41"/>
+      <c r="H1" s="41"/>
+      <c r="I1" s="41"/>
+      <c r="J1" s="41"/>
+      <c r="K1" s="41"/>
+      <c r="L1" s="41"/>
+      <c r="M1" s="41"/>
+      <c r="N1" s="41"/>
+      <c r="O1" s="41"/>
+      <c r="P1" s="41"/>
+      <c r="Q1" s="41"/>
+      <c r="R1" s="41"/>
     </row>
     <row r="3" spans="1:18" ht="16" x14ac:dyDescent="0.25">
-      <c r="A3" s="38" t="s">
+      <c r="A3" s="42" t="s">
         <v>40</v>
       </c>
-      <c r="B3" s="38"/>
-      <c r="C3" s="38"/>
-      <c r="D3" s="38"/>
-      <c r="E3" s="38"/>
-      <c r="F3" s="38"/>
+      <c r="B3" s="42"/>
+      <c r="C3" s="42"/>
+      <c r="D3" s="42"/>
+      <c r="E3" s="42"/>
+      <c r="F3" s="42"/>
     </row>
     <row r="5" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A5" t="s">
@@ -2315,13 +2338,13 @@
       </c>
     </row>
     <row r="25" spans="1:9" ht="19" x14ac:dyDescent="0.25">
-      <c r="A25" s="39" t="s">
+      <c r="A25" s="43" t="s">
         <v>49</v>
       </c>
-      <c r="B25" s="39"/>
-      <c r="C25" s="39"/>
-      <c r="D25" s="39"/>
-      <c r="E25" s="39"/>
+      <c r="B25" s="43"/>
+      <c r="C25" s="43"/>
+      <c r="D25" s="43"/>
+      <c r="E25" s="43"/>
     </row>
     <row r="27" spans="1:9" x14ac:dyDescent="0.2">
       <c r="B27" s="7" t="s">
@@ -2343,16 +2366,19 @@
       <c r="B29" s="7" t="s">
         <v>11</v>
       </c>
-      <c r="C29" s="8"/>
+      <c r="C29" s="8" cm="1">
+        <f t="array" ref="C29">INDEX(A17:F22,MATCH(C27,A17:A22,0),MATCH(C28,B16:E16,0)+1)</f>
+        <v>54</v>
+      </c>
     </row>
     <row r="31" spans="1:9" ht="19" x14ac:dyDescent="0.25">
-      <c r="A31" s="39" t="s">
+      <c r="A31" s="43" t="s">
         <v>51</v>
       </c>
-      <c r="B31" s="39"/>
-      <c r="C31" s="39"/>
-      <c r="D31" s="39"/>
-      <c r="E31" s="39"/>
+      <c r="B31" s="43"/>
+      <c r="C31" s="43"/>
+      <c r="D31" s="43"/>
+      <c r="E31" s="43"/>
     </row>
     <row r="33" spans="2:3" x14ac:dyDescent="0.2">
       <c r="B33" s="7" t="s">
@@ -2366,13 +2392,19 @@
       <c r="B34" s="7" t="s">
         <v>26</v>
       </c>
-      <c r="C34" s="2"/>
+      <c r="C34" s="2">
+        <f>VLOOKUP(C33,A17:F22,6,FALSE)</f>
+        <v>171</v>
+      </c>
     </row>
     <row r="35" spans="2:3" x14ac:dyDescent="0.2">
       <c r="B35" s="7" t="s">
         <v>11</v>
       </c>
-      <c r="C35" s="2"/>
+      <c r="C35" s="2">
+        <f>VLOOKUP(C33,A16:F22,5,FALSE)</f>
+        <v>45</v>
+      </c>
     </row>
   </sheetData>
   <mergeCells count="4">
@@ -2395,7 +2427,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="B2:G12"/>
+  <dimension ref="B2:G13"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="2" max="2" width="15.5" bestFit="1" customWidth="1"/>
@@ -2404,13 +2436,13 @@
   </cols>
   <sheetData>
     <row r="2" spans="2:7" x14ac:dyDescent="0.2">
-      <c r="B2" s="40" t="s">
+      <c r="B2" s="44" t="s">
         <v>52</v>
       </c>
-      <c r="C2" s="40"/>
-      <c r="D2" s="40"/>
-      <c r="E2" s="40"/>
-      <c r="F2" s="40"/>
+      <c r="C2" s="44"/>
+      <c r="D2" s="44"/>
+      <c r="E2" s="44"/>
+      <c r="F2" s="44"/>
     </row>
     <row r="4" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B4" s="1" t="s">
@@ -2536,7 +2568,16 @@
       <c r="C12" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="D12" s="3"/>
+      <c r="D12" s="3">
+        <f>INDEX(C5:G8,MATCH(D10,B5:B8,0),MATCH(D11,C4:G4,0))</f>
+        <v>1.1000000000000001</v>
+      </c>
+    </row>
+    <row r="13" spans="2:7" x14ac:dyDescent="0.2">
+      <c r="D13">
+        <f>INDEX(C5:G8,MATCH(D10,B5:B8,0),MATCH(D11,C4:F4,0))</f>
+        <v>1.1000000000000001</v>
+      </c>
     </row>
   </sheetData>
   <mergeCells count="1">
@@ -2558,151 +2599,151 @@
   </cols>
   <sheetData>
     <row r="2" spans="2:17" x14ac:dyDescent="0.2">
-      <c r="B2" s="41" t="s">
+      <c r="B2" s="45" t="s">
         <v>107</v>
       </c>
-      <c r="C2" s="41"/>
-      <c r="D2" s="41"/>
-      <c r="E2" s="41"/>
-      <c r="F2" s="41"/>
-      <c r="G2" s="41"/>
-      <c r="H2" s="41"/>
-      <c r="I2" s="41"/>
-      <c r="J2" s="41"/>
-      <c r="K2" s="41"/>
-      <c r="L2" s="41"/>
-      <c r="M2" s="41"/>
-      <c r="N2" s="41"/>
-      <c r="O2" s="41"/>
-      <c r="P2" s="41"/>
-      <c r="Q2" s="41"/>
+      <c r="C2" s="45"/>
+      <c r="D2" s="45"/>
+      <c r="E2" s="45"/>
+      <c r="F2" s="45"/>
+      <c r="G2" s="45"/>
+      <c r="H2" s="45"/>
+      <c r="I2" s="45"/>
+      <c r="J2" s="45"/>
+      <c r="K2" s="45"/>
+      <c r="L2" s="45"/>
+      <c r="M2" s="45"/>
+      <c r="N2" s="45"/>
+      <c r="O2" s="45"/>
+      <c r="P2" s="45"/>
+      <c r="Q2" s="45"/>
     </row>
     <row r="3" spans="2:17" x14ac:dyDescent="0.2">
-      <c r="B3" s="41"/>
-      <c r="C3" s="41"/>
-      <c r="D3" s="41"/>
-      <c r="E3" s="41"/>
-      <c r="F3" s="41"/>
-      <c r="G3" s="41"/>
-      <c r="H3" s="41"/>
-      <c r="I3" s="41"/>
-      <c r="J3" s="41"/>
-      <c r="K3" s="41"/>
-      <c r="L3" s="41"/>
-      <c r="M3" s="41"/>
-      <c r="N3" s="41"/>
-      <c r="O3" s="41"/>
-      <c r="P3" s="41"/>
-      <c r="Q3" s="41"/>
+      <c r="B3" s="45"/>
+      <c r="C3" s="45"/>
+      <c r="D3" s="45"/>
+      <c r="E3" s="45"/>
+      <c r="F3" s="45"/>
+      <c r="G3" s="45"/>
+      <c r="H3" s="45"/>
+      <c r="I3" s="45"/>
+      <c r="J3" s="45"/>
+      <c r="K3" s="45"/>
+      <c r="L3" s="45"/>
+      <c r="M3" s="45"/>
+      <c r="N3" s="45"/>
+      <c r="O3" s="45"/>
+      <c r="P3" s="45"/>
+      <c r="Q3" s="45"/>
     </row>
     <row r="4" spans="2:17" x14ac:dyDescent="0.2">
-      <c r="B4" s="41"/>
-      <c r="C4" s="41"/>
-      <c r="D4" s="41"/>
-      <c r="E4" s="41"/>
-      <c r="F4" s="41"/>
-      <c r="G4" s="41"/>
-      <c r="H4" s="41"/>
-      <c r="I4" s="41"/>
-      <c r="J4" s="41"/>
-      <c r="K4" s="41"/>
-      <c r="L4" s="41"/>
-      <c r="M4" s="41"/>
-      <c r="N4" s="41"/>
-      <c r="O4" s="41"/>
-      <c r="P4" s="41"/>
-      <c r="Q4" s="41"/>
+      <c r="B4" s="45"/>
+      <c r="C4" s="45"/>
+      <c r="D4" s="45"/>
+      <c r="E4" s="45"/>
+      <c r="F4" s="45"/>
+      <c r="G4" s="45"/>
+      <c r="H4" s="45"/>
+      <c r="I4" s="45"/>
+      <c r="J4" s="45"/>
+      <c r="K4" s="45"/>
+      <c r="L4" s="45"/>
+      <c r="M4" s="45"/>
+      <c r="N4" s="45"/>
+      <c r="O4" s="45"/>
+      <c r="P4" s="45"/>
+      <c r="Q4" s="45"/>
     </row>
     <row r="5" spans="2:17" x14ac:dyDescent="0.2">
-      <c r="B5" s="41"/>
-      <c r="C5" s="41"/>
-      <c r="D5" s="41"/>
-      <c r="E5" s="41"/>
-      <c r="F5" s="41"/>
-      <c r="G5" s="41"/>
-      <c r="H5" s="41"/>
-      <c r="I5" s="41"/>
-      <c r="J5" s="41"/>
-      <c r="K5" s="41"/>
-      <c r="L5" s="41"/>
-      <c r="M5" s="41"/>
-      <c r="N5" s="41"/>
-      <c r="O5" s="41"/>
-      <c r="P5" s="41"/>
-      <c r="Q5" s="41"/>
+      <c r="B5" s="45"/>
+      <c r="C5" s="45"/>
+      <c r="D5" s="45"/>
+      <c r="E5" s="45"/>
+      <c r="F5" s="45"/>
+      <c r="G5" s="45"/>
+      <c r="H5" s="45"/>
+      <c r="I5" s="45"/>
+      <c r="J5" s="45"/>
+      <c r="K5" s="45"/>
+      <c r="L5" s="45"/>
+      <c r="M5" s="45"/>
+      <c r="N5" s="45"/>
+      <c r="O5" s="45"/>
+      <c r="P5" s="45"/>
+      <c r="Q5" s="45"/>
     </row>
     <row r="7" spans="2:17" x14ac:dyDescent="0.2">
-      <c r="B7" s="42" t="s">
+      <c r="B7" s="46" t="s">
         <v>53</v>
       </c>
-      <c r="C7" s="42"/>
-      <c r="D7" s="42"/>
-      <c r="E7" s="42"/>
-      <c r="F7" s="42"/>
-      <c r="G7" s="42"/>
-      <c r="H7" s="42"/>
-      <c r="I7" s="42"/>
-      <c r="J7" s="42"/>
-      <c r="K7" s="42"/>
-      <c r="L7" s="42"/>
-      <c r="M7" s="42"/>
-      <c r="N7" s="42"/>
-      <c r="O7" s="42"/>
-      <c r="P7" s="42"/>
-      <c r="Q7" s="42"/>
+      <c r="C7" s="46"/>
+      <c r="D7" s="46"/>
+      <c r="E7" s="46"/>
+      <c r="F7" s="46"/>
+      <c r="G7" s="46"/>
+      <c r="H7" s="46"/>
+      <c r="I7" s="46"/>
+      <c r="J7" s="46"/>
+      <c r="K7" s="46"/>
+      <c r="L7" s="46"/>
+      <c r="M7" s="46"/>
+      <c r="N7" s="46"/>
+      <c r="O7" s="46"/>
+      <c r="P7" s="46"/>
+      <c r="Q7" s="46"/>
     </row>
     <row r="8" spans="2:17" x14ac:dyDescent="0.2">
-      <c r="B8" s="42"/>
-      <c r="C8" s="42"/>
-      <c r="D8" s="42"/>
-      <c r="E8" s="42"/>
-      <c r="F8" s="42"/>
-      <c r="G8" s="42"/>
-      <c r="H8" s="42"/>
-      <c r="I8" s="42"/>
-      <c r="J8" s="42"/>
-      <c r="K8" s="42"/>
-      <c r="L8" s="42"/>
-      <c r="M8" s="42"/>
-      <c r="N8" s="42"/>
-      <c r="O8" s="42"/>
-      <c r="P8" s="42"/>
-      <c r="Q8" s="42"/>
+      <c r="B8" s="46"/>
+      <c r="C8" s="46"/>
+      <c r="D8" s="46"/>
+      <c r="E8" s="46"/>
+      <c r="F8" s="46"/>
+      <c r="G8" s="46"/>
+      <c r="H8" s="46"/>
+      <c r="I8" s="46"/>
+      <c r="J8" s="46"/>
+      <c r="K8" s="46"/>
+      <c r="L8" s="46"/>
+      <c r="M8" s="46"/>
+      <c r="N8" s="46"/>
+      <c r="O8" s="46"/>
+      <c r="P8" s="46"/>
+      <c r="Q8" s="46"/>
     </row>
     <row r="9" spans="2:17" x14ac:dyDescent="0.2">
-      <c r="B9" s="42"/>
-      <c r="C9" s="42"/>
-      <c r="D9" s="42"/>
-      <c r="E9" s="42"/>
-      <c r="F9" s="42"/>
-      <c r="G9" s="42"/>
-      <c r="H9" s="42"/>
-      <c r="I9" s="42"/>
-      <c r="J9" s="42"/>
-      <c r="K9" s="42"/>
-      <c r="L9" s="42"/>
-      <c r="M9" s="42"/>
-      <c r="N9" s="42"/>
-      <c r="O9" s="42"/>
-      <c r="P9" s="42"/>
-      <c r="Q9" s="42"/>
-    </row>
-    <row r="11" spans="2:17" ht="16" x14ac:dyDescent="0.2">
-      <c r="B11" s="43" t="s">
+      <c r="B9" s="46"/>
+      <c r="C9" s="46"/>
+      <c r="D9" s="46"/>
+      <c r="E9" s="46"/>
+      <c r="F9" s="46"/>
+      <c r="G9" s="46"/>
+      <c r="H9" s="46"/>
+      <c r="I9" s="46"/>
+      <c r="J9" s="46"/>
+      <c r="K9" s="46"/>
+      <c r="L9" s="46"/>
+      <c r="M9" s="46"/>
+      <c r="N9" s="46"/>
+      <c r="O9" s="46"/>
+      <c r="P9" s="46"/>
+      <c r="Q9" s="46"/>
+    </row>
+    <row r="11" spans="2:17" ht="20" x14ac:dyDescent="0.2">
+      <c r="B11" s="47" t="s">
         <v>54</v>
       </c>
-      <c r="C11" s="43"/>
-      <c r="D11" s="43"/>
-      <c r="F11" s="44" t="s">
+      <c r="C11" s="47"/>
+      <c r="D11" s="47"/>
+      <c r="F11" s="48" t="s">
         <v>55</v>
       </c>
-      <c r="G11" s="44"/>
-      <c r="H11" s="44"/>
-      <c r="I11" s="44"/>
-      <c r="J11" s="44"/>
-      <c r="K11" s="44"/>
-      <c r="L11" s="44"/>
-      <c r="M11" s="44"/>
+      <c r="G11" s="48"/>
+      <c r="H11" s="48"/>
+      <c r="I11" s="48"/>
+      <c r="J11" s="48"/>
+      <c r="K11" s="48"/>
+      <c r="L11" s="48"/>
+      <c r="M11" s="48"/>
     </row>
     <row r="13" spans="2:17" x14ac:dyDescent="0.2">
       <c r="B13" t="s">
@@ -2788,8 +2829,14 @@
       <c r="F26" s="3">
         <v>4</v>
       </c>
-      <c r="G26" s="3"/>
-      <c r="H26" s="3"/>
+      <c r="G26" s="3" t="str">
+        <f>VLOOKUP(F26,$B$25:$D$34,2,FALSE)</f>
+        <v>Elk</v>
+      </c>
+      <c r="H26" s="3">
+        <f>VLOOKUP(F26,$B$24:$D$34,3,FALSE)</f>
+        <v>45</v>
+      </c>
     </row>
     <row r="27" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B27" s="2">
@@ -2804,8 +2851,14 @@
       <c r="F27" s="3">
         <v>5</v>
       </c>
-      <c r="G27" s="3"/>
-      <c r="H27" s="3"/>
+      <c r="G27" s="3" t="str">
+        <f t="shared" ref="G27:G28" si="0">VLOOKUP(F27,$B$25:$D$34,2,FALSE)</f>
+        <v>Coyote</v>
+      </c>
+      <c r="H27" s="3">
+        <f t="shared" ref="H27:H29" si="1">VLOOKUP(F27,$B$24:$D$34,3,FALSE)</f>
+        <v>43</v>
+      </c>
     </row>
     <row r="28" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B28" s="2">
@@ -2820,8 +2873,14 @@
       <c r="F28" s="3">
         <v>7</v>
       </c>
-      <c r="G28" s="3"/>
-      <c r="H28" s="3"/>
+      <c r="G28" s="3" t="str">
+        <f t="shared" si="0"/>
+        <v>Ostrich</v>
+      </c>
+      <c r="H28" s="3">
+        <f t="shared" si="1"/>
+        <v>40</v>
+      </c>
     </row>
     <row r="29" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B29" s="2">
@@ -2836,8 +2895,14 @@
       <c r="F29" s="3">
         <v>2</v>
       </c>
-      <c r="G29" s="3"/>
-      <c r="H29" s="3"/>
+      <c r="G29" s="3" t="str">
+        <f>VLOOKUP(F29,$B$25:$D$34,2,FALSE)</f>
+        <v>Antelope</v>
+      </c>
+      <c r="H29" s="3">
+        <f t="shared" si="1"/>
+        <v>61</v>
+      </c>
     </row>
     <row r="30" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B30" s="2">
@@ -2923,77 +2988,77 @@
   </cols>
   <sheetData>
     <row r="2" spans="2:17" x14ac:dyDescent="0.2">
-      <c r="B2" s="41" t="s">
+      <c r="B2" s="45" t="s">
         <v>108</v>
       </c>
-      <c r="C2" s="41"/>
-      <c r="D2" s="41"/>
-      <c r="E2" s="41"/>
-      <c r="F2" s="41"/>
-      <c r="G2" s="41"/>
-      <c r="H2" s="41"/>
-      <c r="I2" s="41"/>
-      <c r="J2" s="41"/>
-      <c r="K2" s="41"/>
-      <c r="L2" s="41"/>
-      <c r="M2" s="41"/>
-      <c r="N2" s="41"/>
-      <c r="O2" s="41"/>
-      <c r="P2" s="41"/>
-      <c r="Q2" s="41"/>
+      <c r="C2" s="45"/>
+      <c r="D2" s="45"/>
+      <c r="E2" s="45"/>
+      <c r="F2" s="45"/>
+      <c r="G2" s="45"/>
+      <c r="H2" s="45"/>
+      <c r="I2" s="45"/>
+      <c r="J2" s="45"/>
+      <c r="K2" s="45"/>
+      <c r="L2" s="45"/>
+      <c r="M2" s="45"/>
+      <c r="N2" s="45"/>
+      <c r="O2" s="45"/>
+      <c r="P2" s="45"/>
+      <c r="Q2" s="45"/>
     </row>
     <row r="3" spans="2:17" x14ac:dyDescent="0.2">
-      <c r="B3" s="41"/>
-      <c r="C3" s="41"/>
-      <c r="D3" s="41"/>
-      <c r="E3" s="41"/>
-      <c r="F3" s="41"/>
-      <c r="G3" s="41"/>
-      <c r="H3" s="41"/>
-      <c r="I3" s="41"/>
-      <c r="J3" s="41"/>
-      <c r="K3" s="41"/>
-      <c r="L3" s="41"/>
-      <c r="M3" s="41"/>
-      <c r="N3" s="41"/>
-      <c r="O3" s="41"/>
-      <c r="P3" s="41"/>
-      <c r="Q3" s="41"/>
+      <c r="B3" s="45"/>
+      <c r="C3" s="45"/>
+      <c r="D3" s="45"/>
+      <c r="E3" s="45"/>
+      <c r="F3" s="45"/>
+      <c r="G3" s="45"/>
+      <c r="H3" s="45"/>
+      <c r="I3" s="45"/>
+      <c r="J3" s="45"/>
+      <c r="K3" s="45"/>
+      <c r="L3" s="45"/>
+      <c r="M3" s="45"/>
+      <c r="N3" s="45"/>
+      <c r="O3" s="45"/>
+      <c r="P3" s="45"/>
+      <c r="Q3" s="45"/>
     </row>
     <row r="4" spans="2:17" x14ac:dyDescent="0.2">
-      <c r="B4" s="41"/>
-      <c r="C4" s="41"/>
-      <c r="D4" s="41"/>
-      <c r="E4" s="41"/>
-      <c r="F4" s="41"/>
-      <c r="G4" s="41"/>
-      <c r="H4" s="41"/>
-      <c r="I4" s="41"/>
-      <c r="J4" s="41"/>
-      <c r="K4" s="41"/>
-      <c r="L4" s="41"/>
-      <c r="M4" s="41"/>
-      <c r="N4" s="41"/>
-      <c r="O4" s="41"/>
-      <c r="P4" s="41"/>
-      <c r="Q4" s="41"/>
-    </row>
-    <row r="6" spans="2:17" ht="16" x14ac:dyDescent="0.2">
-      <c r="B6" s="43" t="s">
+      <c r="B4" s="45"/>
+      <c r="C4" s="45"/>
+      <c r="D4" s="45"/>
+      <c r="E4" s="45"/>
+      <c r="F4" s="45"/>
+      <c r="G4" s="45"/>
+      <c r="H4" s="45"/>
+      <c r="I4" s="45"/>
+      <c r="J4" s="45"/>
+      <c r="K4" s="45"/>
+      <c r="L4" s="45"/>
+      <c r="M4" s="45"/>
+      <c r="N4" s="45"/>
+      <c r="O4" s="45"/>
+      <c r="P4" s="45"/>
+      <c r="Q4" s="45"/>
+    </row>
+    <row r="6" spans="2:17" ht="20" x14ac:dyDescent="0.2">
+      <c r="B6" s="47" t="s">
         <v>78</v>
       </c>
-      <c r="C6" s="43"/>
-      <c r="D6" s="43"/>
-      <c r="F6" s="44" t="s">
+      <c r="C6" s="47"/>
+      <c r="D6" s="47"/>
+      <c r="F6" s="48" t="s">
         <v>79</v>
       </c>
-      <c r="G6" s="44"/>
-      <c r="H6" s="44"/>
-      <c r="I6" s="44"/>
-      <c r="J6" s="44"/>
-      <c r="K6" s="44"/>
-      <c r="L6" s="44"/>
-      <c r="M6" s="44"/>
+      <c r="G6" s="48"/>
+      <c r="H6" s="48"/>
+      <c r="I6" s="48"/>
+      <c r="J6" s="48"/>
+      <c r="K6" s="48"/>
+      <c r="L6" s="48"/>
+      <c r="M6" s="48"/>
     </row>
     <row r="7" spans="2:17" ht="16.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B7" s="17"/>
@@ -3277,31 +3342,31 @@
         <v>95</v>
       </c>
       <c r="B3" s="31">
-        <f>HLOOKUP(B1,Diameter,MATCH($A$3,planetall,0),FALSE)</f>
+        <f t="shared" ref="B3:H3" si="0">HLOOKUP(B1,Diameter,MATCH($A$3,planetall,0),FALSE)</f>
         <v>4878</v>
       </c>
       <c r="C3" s="31">
-        <f>HLOOKUP(C1,Diameter,MATCH($A$3,planetall,0),FALSE)</f>
+        <f t="shared" si="0"/>
         <v>12104</v>
       </c>
       <c r="D3" s="31">
-        <f>HLOOKUP(D1,Diameter,MATCH($A$3,planetall,0),FALSE)</f>
+        <f t="shared" si="0"/>
         <v>12755</v>
       </c>
       <c r="E3" s="31">
-        <f>HLOOKUP(E1,Diameter,MATCH($A$3,planetall,0),FALSE)</f>
+        <f t="shared" si="0"/>
         <v>6790</v>
       </c>
       <c r="F3" s="31">
-        <f>HLOOKUP(F1,Diameter,MATCH($A$3,planetall,0),FALSE)</f>
+        <f t="shared" si="0"/>
         <v>142796</v>
       </c>
       <c r="G3" s="31">
-        <f>HLOOKUP(G1,Diameter,MATCH($A$3,planetall,0),FALSE)</f>
+        <f t="shared" si="0"/>
         <v>120660</v>
       </c>
       <c r="H3" s="31">
-        <f>HLOOKUP(H1,Diameter,MATCH($A$3,planetall,0),FALSE)</f>
+        <f t="shared" si="0"/>
         <v>51118</v>
       </c>
       <c r="I3" s="31">
@@ -3310,19 +3375,28 @@
       </c>
     </row>
     <row r="12" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="B12" s="46" t="s">
+      <c r="B12" s="33" t="s">
         <v>86</v>
       </c>
       <c r="C12" t="s">
-        <v>90</v>
+        <v>92</v>
       </c>
     </row>
     <row r="13" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="B13" s="46" t="s">
+      <c r="B13" s="33" t="s">
         <v>95</v>
       </c>
+      <c r="C13">
+        <f>HLOOKUP('HLOOKUP another sheet'!C12,Diameter,2,FALSE)</f>
+        <v>120660</v>
+      </c>
     </row>
   </sheetData>
+  <dataValidations count="1">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="C12" xr:uid="{D041779D-F235-F342-830B-257C68CD44A5}">
+      <formula1>$B$1:$I$1</formula1>
+    </dataValidation>
+  </dataValidations>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <drawing r:id="rId1"/>
 </worksheet>
@@ -3335,6 +3409,7 @@
   <cols>
     <col min="2" max="2" width="15.83203125" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="11.6640625" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="11.33203125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="3" spans="2:9" ht="16" x14ac:dyDescent="0.2">
@@ -3359,13 +3434,22 @@
       <c r="B5" s="23" t="s">
         <v>97</v>
       </c>
-      <c r="C5" s="24"/>
+      <c r="C5" s="24">
+        <f ca="1">SUM(OFFSET(B7,1,3,5))</f>
+        <v>20400</v>
+      </c>
       <c r="D5" s="25"/>
       <c r="E5" s="25" t="s">
         <v>117</v>
       </c>
-      <c r="F5" s="25"/>
+      <c r="F5" s="25">
+        <f ca="1">SUM(OFFSET(B7,1,1,5,5))</f>
+        <v>84000</v>
+      </c>
       <c r="G5" s="25"/>
+      <c r="H5" t="s">
+        <v>119</v>
+      </c>
     </row>
     <row r="6" spans="2:9" ht="16" x14ac:dyDescent="0.2">
       <c r="B6" s="23"/>
@@ -3374,6 +3458,10 @@
       <c r="E6" s="23"/>
       <c r="F6" s="23"/>
       <c r="G6" s="23"/>
+      <c r="H6">
+        <f ca="1">SUM(OFFSET(B7,1,1,1,5))</f>
+        <v>24500</v>
+      </c>
       <c r="I6" s="32"/>
     </row>
     <row r="7" spans="2:9" ht="16" x14ac:dyDescent="0.2">
@@ -3626,11 +3714,11 @@
       <c r="G21" s="23"/>
     </row>
     <row r="22" spans="2:7" ht="16" x14ac:dyDescent="0.2">
-      <c r="B22" s="45" t="s">
+      <c r="B22" s="36" t="s">
         <v>106</v>
       </c>
       <c r="C22" s="30">
-        <f ca="1">OFFSET(G15,3,-4)</f>
+        <f ca="1">OFFSET(B15,3,1)</f>
         <v>2500</v>
       </c>
       <c r="D22" s="23"/>
@@ -3639,7 +3727,10 @@
       <c r="G22" s="23"/>
     </row>
     <row r="23" spans="2:7" x14ac:dyDescent="0.2">
-      <c r="B23" s="45"/>
+      <c r="B23" s="36"/>
+      <c r="C23" t="s">
+        <v>118</v>
+      </c>
     </row>
   </sheetData>
   <mergeCells count="1">
